--- a/research/traditional_assets/database/data/tunisia/tunisia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0936</v>
+        <v>0.06630000000000001</v>
       </c>
       <c r="E2">
-        <v>0.01335</v>
+        <v>0.07715000000000001</v>
       </c>
       <c r="G2">
-        <v>0.5439778379399358</v>
+        <v>0.5861010326542004</v>
       </c>
       <c r="H2">
-        <v>0.5439778379399358</v>
+        <v>0.5861010326542004</v>
       </c>
       <c r="I2">
-        <v>0.5238305106088271</v>
+        <v>0.5295841473625454</v>
       </c>
       <c r="J2">
-        <v>0.3492637711908341</v>
+        <v>0.350043345514941</v>
       </c>
       <c r="K2">
-        <v>12.15</v>
+        <v>14.37</v>
       </c>
       <c r="L2">
-        <v>0.07649688346030348</v>
+        <v>0.1002651409433436</v>
       </c>
       <c r="M2">
-        <v>2.604</v>
+        <v>8.064</v>
       </c>
       <c r="N2">
-        <v>0.02864686468646865</v>
+        <v>0.08211812627291243</v>
       </c>
       <c r="O2">
-        <v>0.214320987654321</v>
+        <v>0.561169102296451</v>
       </c>
       <c r="P2">
-        <v>2.604</v>
+        <v>8.064</v>
       </c>
       <c r="Q2">
-        <v>0.02864686468646865</v>
+        <v>0.08211812627291243</v>
       </c>
       <c r="R2">
-        <v>0.214320987654321</v>
+        <v>0.561169102296451</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>30.2</v>
+        <v>22.5</v>
       </c>
       <c r="V2">
-        <v>0.3322332233223322</v>
-      </c>
-      <c r="W2">
-        <v>0.1475611712795828</v>
+        <v>0.2291242362525458</v>
       </c>
       <c r="X2">
-        <v>0.1526210943157558</v>
-      </c>
-      <c r="Y2">
-        <v>-0.005059923036172947</v>
+        <v>0.1755239935357646</v>
       </c>
       <c r="Z2">
-        <v>0.3450725645259407</v>
-      </c>
-      <c r="AA2">
-        <v>0.06246020593540509</v>
+        <v>0.5300099848378389</v>
       </c>
       <c r="AB2">
-        <v>0.0871075806226172</v>
-      </c>
-      <c r="AC2">
-        <v>-0.02542239413902419</v>
+        <v>0.133086125087702</v>
       </c>
       <c r="AD2">
-        <v>405.1</v>
+        <v>339.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>405.1</v>
+        <v>339.4</v>
       </c>
       <c r="AG2">
-        <v>374.9</v>
+        <v>316.9</v>
       </c>
       <c r="AH2">
-        <v>0.816733870967742</v>
+        <v>0.7755941499085923</v>
       </c>
       <c r="AI2">
-        <v>0.8162401773121096</v>
+        <v>0.7957796014067995</v>
       </c>
       <c r="AJ2">
-        <v>0.804851867754401</v>
+        <v>0.7634304986750181</v>
       </c>
       <c r="AK2">
-        <v>0.8043338339412144</v>
+        <v>0.7844059405940593</v>
       </c>
       <c r="AL2">
-        <v>67.8</v>
+        <v>56.3</v>
       </c>
       <c r="AM2">
-        <v>67.355</v>
+        <v>54.90000000000001</v>
       </c>
       <c r="AN2">
-        <v>4.661680092059838</v>
+        <v>4.133982947624848</v>
       </c>
       <c r="AO2">
-        <v>1.227138643067847</v>
+        <v>1.348134991119005</v>
       </c>
       <c r="AP2">
-        <v>4.31415420023015</v>
+        <v>3.859926918392205</v>
       </c>
       <c r="AQ2">
-        <v>1.235246084180833</v>
+        <v>1.382513661202186</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tunisie Leasing &amp; Factoring Société anonyme (BVMT:TLS)</t>
+          <t>Arab Tunisian Lease S.A. (BVMT:ATL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +710,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07820000000000001</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="E3">
-        <v>-0.08740000000000001</v>
+        <v>0.09880000000000001</v>
       </c>
       <c r="G3">
-        <v>0.4937679769894535</v>
+        <v>0.7114624505928854</v>
       </c>
       <c r="H3">
-        <v>0.4937679769894535</v>
+        <v>0.7114624505928854</v>
       </c>
       <c r="I3">
-        <v>0.4621284755512944</v>
+        <v>0.6837944664031621</v>
       </c>
       <c r="J3">
-        <v>0.2559401879024372</v>
+        <v>0.4750453306200186</v>
       </c>
       <c r="K3">
-        <v>3.33</v>
+        <v>4.22</v>
       </c>
       <c r="L3">
-        <v>0.03192713326941515</v>
+        <v>0.166798418972332</v>
       </c>
       <c r="M3">
-        <v>0.003</v>
+        <v>2.11</v>
       </c>
       <c r="N3">
-        <v>8.823529411764706e-05</v>
+        <v>0.06719745222929936</v>
       </c>
       <c r="O3">
-        <v>0.0009009009009009009</v>
+        <v>0.5</v>
       </c>
       <c r="P3">
-        <v>0.003</v>
+        <v>2.11</v>
       </c>
       <c r="Q3">
-        <v>8.823529411764706e-05</v>
+        <v>0.06719745222929936</v>
       </c>
       <c r="R3">
-        <v>0.0009009009009009009</v>
+        <v>0.5</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,52 +758,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.1031847133757962</v>
       </c>
       <c r="X3">
-        <v>0.03746812331368842</v>
+        <v>0.1728978522524446</v>
       </c>
       <c r="AB3">
-        <v>0.03746812331368842</v>
+        <v>0.1367351325325558</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>129.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>129.5</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>126.26</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.8048477315102548</v>
+      </c>
+      <c r="AI3">
+        <v>0.7848484848484848</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.800837244703793</v>
+      </c>
+      <c r="AK3">
+        <v>0.7805390702274976</v>
       </c>
       <c r="AL3">
-        <v>41.9</v>
+        <v>10.2</v>
       </c>
       <c r="AM3">
-        <v>41.9</v>
+        <v>8.799999999999999</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>7.442528735632185</v>
       </c>
       <c r="AO3">
-        <v>1.15035799522673</v>
+        <v>1.696078431372549</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>7.256321839080461</v>
       </c>
       <c r="AQ3">
-        <v>1.15035799522673</v>
+        <v>1.965909090909091</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Attijari Leasing S.A. (BVMT:TJL)</t>
+          <t>Tunisie Leasing &amp; Factoring Société anonyme (BVMT:TLS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,46 +829,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.066</v>
+        <v>0.0444</v>
       </c>
       <c r="E4">
-        <v>0.068</v>
+        <v>-0.0255</v>
       </c>
       <c r="G4">
-        <v>0.7429906542056075</v>
+        <v>0.5613259668508287</v>
       </c>
       <c r="H4">
-        <v>0.7429906542056075</v>
+        <v>0.5613259668508287</v>
       </c>
       <c r="I4">
-        <v>0.7570093457943925</v>
+        <v>0.4950276243093922</v>
       </c>
       <c r="J4">
-        <v>0.5539313895573339</v>
+        <v>0.2475138121546961</v>
       </c>
       <c r="K4">
-        <v>2.44</v>
+        <v>3.84</v>
       </c>
       <c r="L4">
-        <v>0.1140186915887851</v>
+        <v>0.04243093922651934</v>
       </c>
       <c r="M4">
-        <v>0.495</v>
+        <v>4.26</v>
       </c>
       <c r="N4">
-        <v>0.04304347826086957</v>
+        <v>0.1302752293577981</v>
       </c>
       <c r="O4">
-        <v>0.2028688524590164</v>
+        <v>1.109375</v>
       </c>
       <c r="P4">
-        <v>0.495</v>
+        <v>4.26</v>
       </c>
       <c r="Q4">
-        <v>0.04304347826086957</v>
+        <v>0.1302752293577981</v>
       </c>
       <c r="R4">
-        <v>0.2028688524590164</v>
+        <v>1.109375</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,73 +877,52 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.3904347826086957</v>
-      </c>
-      <c r="W4">
-        <v>0.1355555555555555</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.2666149587559173</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1310594032003617</v>
-      </c>
-      <c r="Z4">
-        <v>0.1296969696969697</v>
-      </c>
-      <c r="AA4">
-        <v>0.07184322264561786</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AB4">
-        <v>0.08881694245278396</v>
-      </c>
-      <c r="AC4">
-        <v>-0.0169737198071661</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AD4">
-        <v>138.6</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>138.6</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>134.11</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.9233844103930713</v>
-      </c>
-      <c r="AI4">
-        <v>0.8711502199874293</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.9210219078360002</v>
-      </c>
-      <c r="AK4">
-        <v>0.8674083177026065</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>12.8</v>
+        <v>35.7</v>
       </c>
       <c r="AM4">
-        <v>12.8</v>
+        <v>35.7</v>
       </c>
       <c r="AN4">
-        <v>8.451219512195122</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>1.265625</v>
+        <v>1.254901960784313</v>
       </c>
       <c r="AP4">
-        <v>8.177439024390244</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1.265625</v>
+        <v>1.254901960784313</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arab Tunisian Lease S.A. (BVMT:ATL)</t>
+          <t>Attijari Leasing S.A. (BVMT:TJL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,121 +942,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.109</v>
+        <v>0.0445</v>
       </c>
       <c r="E5">
-        <v>-0.0413</v>
+        <v>0.0555</v>
       </c>
       <c r="G5">
-        <v>0.7307692307692307</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="H5">
-        <v>0.7307692307692307</v>
+        <v>0.7835051546391752</v>
       </c>
       <c r="I5">
-        <v>0.7230769230769231</v>
+        <v>0.7113402061855671</v>
       </c>
       <c r="J5">
-        <v>0.3947718020141418</v>
+        <v>0.5078638216255096</v>
       </c>
       <c r="K5">
+        <v>2.45</v>
+      </c>
+      <c r="L5">
+        <v>0.1262886597938145</v>
+      </c>
+      <c r="M5">
+        <v>0.624</v>
+      </c>
+      <c r="N5">
+        <v>0.0515702479338843</v>
+      </c>
+      <c r="O5">
+        <v>0.2546938775510204</v>
+      </c>
+      <c r="P5">
+        <v>0.624</v>
+      </c>
+      <c r="Q5">
+        <v>0.0515702479338843</v>
+      </c>
+      <c r="R5">
+        <v>0.2546938775510204</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>1.96</v>
       </c>
-      <c r="L5">
-        <v>0.07538461538461538</v>
-      </c>
-      <c r="M5">
-        <v>0.91</v>
-      </c>
-      <c r="N5">
-        <v>0.04417475728155339</v>
-      </c>
-      <c r="O5">
-        <v>0.4642857142857143</v>
-      </c>
-      <c r="P5">
-        <v>0.91</v>
-      </c>
-      <c r="Q5">
-        <v>0.04417475728155339</v>
-      </c>
-      <c r="R5">
-        <v>0.4642857142857143</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>8.31</v>
-      </c>
       <c r="V5">
-        <v>0.4033980582524272</v>
+        <v>0.1619834710743802</v>
       </c>
       <c r="W5">
-        <v>0.05632183908045978</v>
+        <v>0.1195121951219512</v>
       </c>
       <c r="X5">
-        <v>0.1909557966635149</v>
+        <v>0.3081643867956622</v>
       </c>
       <c r="Y5">
-        <v>-0.1346339575830552</v>
+        <v>-0.188652191673711</v>
       </c>
       <c r="Z5">
-        <v>0.1344503050987693</v>
+        <v>0.1254770066619235</v>
       </c>
       <c r="AA5">
-        <v>0.05307718922519231</v>
+        <v>0.06372523212945402</v>
       </c>
       <c r="AB5">
-        <v>0.08694825769607459</v>
+        <v>0.1451758106807816</v>
       </c>
       <c r="AC5">
-        <v>-0.03387106847088227</v>
+        <v>-0.08145057855132762</v>
       </c>
       <c r="AD5">
-        <v>166.3</v>
+        <v>114.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>166.3</v>
+        <v>114.6</v>
       </c>
       <c r="AG5">
-        <v>157.99</v>
+        <v>112.64</v>
       </c>
       <c r="AH5">
-        <v>0.8897806313536651</v>
+        <v>0.9044988161010261</v>
       </c>
       <c r="AI5">
-        <v>0.8151960784313727</v>
+        <v>0.849518161601186</v>
       </c>
       <c r="AJ5">
-        <v>0.884651996192396</v>
+        <v>0.9029982363315697</v>
       </c>
       <c r="AK5">
-        <v>0.8073483570954061</v>
+        <v>0.8472995336241914</v>
       </c>
       <c r="AL5">
-        <v>13.1</v>
+        <v>10.4</v>
       </c>
       <c r="AM5">
-        <v>12.655</v>
+        <v>10.4</v>
       </c>
       <c r="AN5">
-        <v>8.752631578947369</v>
+        <v>8.244604316546763</v>
       </c>
       <c r="AO5">
-        <v>1.435114503816794</v>
+        <v>1.326923076923077</v>
       </c>
       <c r="AP5">
-        <v>8.315263157894737</v>
+        <v>8.103597122302158</v>
       </c>
       <c r="AQ5">
-        <v>1.485578822599763</v>
+        <v>1.326923076923077</v>
       </c>
     </row>
     <row r="6">
@@ -1103,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.145</v>
+        <v>0.134</v>
       </c>
       <c r="E6">
-        <v>0.187</v>
+        <v>0.134</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1121,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>4.42</v>
+        <v>3.86</v>
       </c>
       <c r="L6">
-        <v>0.6199158485273493</v>
+        <v>0.4753694581280788</v>
       </c>
       <c r="M6">
-        <v>1.196</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>0.0482258064516129</v>
+        <v>0.04863636363636364</v>
       </c>
       <c r="O6">
-        <v>0.2705882352941176</v>
+        <v>0.2772020725388601</v>
       </c>
       <c r="P6">
-        <v>1.196</v>
+        <v>1.07</v>
       </c>
       <c r="Q6">
-        <v>0.0482258064516129</v>
+        <v>0.04863636363636364</v>
       </c>
       <c r="R6">
-        <v>0.2705882352941176</v>
+        <v>0.2772020725388601</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="V6">
-        <v>0.7016129032258064</v>
+        <v>0.7863636363636364</v>
       </c>
       <c r="W6">
-        <v>0.1595667870036101</v>
+        <v>0.116969696969697</v>
       </c>
       <c r="X6">
-        <v>0.1142863919679966</v>
+        <v>0.1781501348190846</v>
       </c>
       <c r="Y6">
-        <v>0.04528039503561351</v>
+        <v>-0.06118043784938763</v>
       </c>
       <c r="Z6">
-        <v>0.06997055937193326</v>
+        <v>0.07012089810017272</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08726690354915979</v>
+        <v>0.1294371176428483</v>
       </c>
       <c r="AC6">
-        <v>-0.08726690354915979</v>
+        <v>-0.1294371176428483</v>
       </c>
       <c r="AD6">
-        <v>100.2</v>
+        <v>95.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>100.2</v>
+        <v>95.3</v>
       </c>
       <c r="AG6">
-        <v>82.80000000000001</v>
+        <v>78</v>
       </c>
       <c r="AH6">
-        <v>0.8016</v>
+        <v>0.8124467178175618</v>
       </c>
       <c r="AI6">
-        <v>0.7522522522522523</v>
+        <v>0.7527646129541864</v>
       </c>
       <c r="AJ6">
-        <v>0.7695167286245354</v>
+        <v>0.78</v>
       </c>
       <c r="AK6">
-        <v>0.7150259067357513</v>
+        <v>0.7136322049405307</v>
       </c>
       <c r="AL6">
         <v>0</v>

--- a/research/traditional_assets/database/data/tunisia/tunisia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_financial_svcs_non_bank_insurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06630000000000001</v>
+        <v>0.0481</v>
       </c>
       <c r="E2">
-        <v>0.07715000000000001</v>
+        <v>0.0992</v>
       </c>
       <c r="G2">
-        <v>0.5861010326542004</v>
+        <v>0.6132577100319037</v>
       </c>
       <c r="H2">
-        <v>0.5861010326542004</v>
+        <v>0.6132577100319037</v>
       </c>
       <c r="I2">
-        <v>0.5295841473625454</v>
+        <v>0.5742644452321872</v>
       </c>
       <c r="J2">
-        <v>0.350043345514941</v>
+        <v>0.3890570124016491</v>
       </c>
       <c r="K2">
-        <v>14.37</v>
+        <v>17.97</v>
       </c>
       <c r="L2">
-        <v>0.1002651409433436</v>
+        <v>0.1274016306274371</v>
       </c>
       <c r="M2">
-        <v>8.064</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N2">
-        <v>0.08211812627291243</v>
+        <v>0.06840775063184498</v>
       </c>
       <c r="O2">
-        <v>0.561169102296451</v>
+        <v>0.4518642181413467</v>
       </c>
       <c r="P2">
-        <v>8.064</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.08211812627291243</v>
+        <v>0.06840775063184498</v>
       </c>
       <c r="R2">
-        <v>0.561169102296451</v>
+        <v>0.4518642181413467</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>22.5</v>
+        <v>18.54</v>
       </c>
       <c r="V2">
-        <v>0.2291242362525458</v>
+        <v>0.1561920808761584</v>
       </c>
       <c r="X2">
-        <v>0.1755239935357646</v>
+        <v>0.1729819400258435</v>
       </c>
       <c r="Z2">
-        <v>0.5300099848378389</v>
+        <v>0.5822737780713341</v>
       </c>
       <c r="AB2">
-        <v>0.133086125087702</v>
+        <v>0.1162967215373642</v>
       </c>
       <c r="AD2">
-        <v>339.4</v>
+        <v>217</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>339.4</v>
+        <v>217</v>
       </c>
       <c r="AG2">
-        <v>316.9</v>
+        <v>198.46</v>
       </c>
       <c r="AH2">
-        <v>0.7755941499085923</v>
+        <v>0.6464104855525767</v>
       </c>
       <c r="AI2">
-        <v>0.7957796014067995</v>
+        <v>0.7977941176470589</v>
       </c>
       <c r="AJ2">
-        <v>0.7634304986750181</v>
+        <v>0.6257409509395888</v>
       </c>
       <c r="AK2">
-        <v>0.7844059405940593</v>
+        <v>0.783003235224493</v>
       </c>
       <c r="AL2">
-        <v>56.3</v>
+        <v>52.79</v>
       </c>
       <c r="AM2">
-        <v>54.90000000000001</v>
+        <v>51.34</v>
       </c>
       <c r="AN2">
-        <v>4.133982947624848</v>
+        <v>2.488532110091743</v>
       </c>
       <c r="AO2">
-        <v>1.348134991119005</v>
+        <v>1.534381511649934</v>
       </c>
       <c r="AP2">
-        <v>3.859926918392205</v>
+        <v>2.27591743119266</v>
       </c>
       <c r="AQ2">
-        <v>1.382513661202186</v>
+        <v>1.577717179587067</v>
       </c>
     </row>
     <row r="3">
@@ -710,46 +710,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08810000000000001</v>
+        <v>0.0649</v>
       </c>
       <c r="E3">
-        <v>0.09880000000000001</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="G3">
-        <v>0.7114624505928854</v>
+        <v>0.7035573122529645</v>
       </c>
       <c r="H3">
-        <v>0.7114624505928854</v>
+        <v>0.7035573122529645</v>
       </c>
       <c r="I3">
-        <v>0.6837944664031621</v>
+        <v>0.6996047430830039</v>
       </c>
       <c r="J3">
-        <v>0.4750453306200186</v>
+        <v>0.4748612504863912</v>
       </c>
       <c r="K3">
-        <v>4.22</v>
+        <v>5.24</v>
       </c>
       <c r="L3">
-        <v>0.166798418972332</v>
+        <v>0.2071146245059289</v>
       </c>
       <c r="M3">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="N3">
-        <v>0.06719745222929936</v>
+        <v>0.05471204188481674</v>
       </c>
       <c r="O3">
-        <v>0.5</v>
+        <v>0.398854961832061</v>
       </c>
       <c r="P3">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="Q3">
-        <v>0.06719745222929936</v>
+        <v>0.05471204188481674</v>
       </c>
       <c r="R3">
-        <v>0.5</v>
+        <v>0.398854961832061</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,58 +758,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.1031847133757962</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.1728978522524446</v>
+        <v>0.08135241227035207</v>
       </c>
       <c r="AB3">
-        <v>0.1367351325325558</v>
+        <v>0.08135241227035207</v>
       </c>
       <c r="AD3">
-        <v>129.5</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>129.5</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>126.26</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.8048477315102548</v>
-      </c>
-      <c r="AI3">
-        <v>0.7848484848484848</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.800837244703793</v>
-      </c>
-      <c r="AK3">
-        <v>0.7805390702274976</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>10.2</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AM3">
-        <v>8.799999999999999</v>
+        <v>7.839999999999999</v>
       </c>
       <c r="AN3">
-        <v>7.442528735632185</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>1.696078431372549</v>
+        <v>1.905274488697524</v>
       </c>
       <c r="AP3">
-        <v>7.256321839080461</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.965909090909091</v>
+        <v>2.25765306122449</v>
       </c>
     </row>
     <row r="4">
@@ -829,46 +823,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0444</v>
+        <v>0.0281</v>
       </c>
       <c r="E4">
-        <v>-0.0255</v>
+        <v>0.118</v>
       </c>
       <c r="G4">
-        <v>0.5613259668508287</v>
+        <v>0.6186152099886493</v>
       </c>
       <c r="H4">
-        <v>0.5613259668508287</v>
+        <v>0.6186152099886493</v>
       </c>
       <c r="I4">
-        <v>0.4950276243093922</v>
+        <v>0.5505107832009081</v>
       </c>
       <c r="J4">
-        <v>0.2475138121546961</v>
+        <v>0.3452541137028212</v>
       </c>
       <c r="K4">
-        <v>3.84</v>
+        <v>6.67</v>
       </c>
       <c r="L4">
-        <v>0.04243093922651934</v>
+        <v>0.0757094211123723</v>
       </c>
       <c r="M4">
-        <v>4.26</v>
+        <v>3.57</v>
       </c>
       <c r="N4">
-        <v>0.1302752293577981</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="O4">
-        <v>1.109375</v>
+        <v>0.5352323838080959</v>
       </c>
       <c r="P4">
-        <v>4.26</v>
+        <v>3.57</v>
       </c>
       <c r="Q4">
-        <v>0.1302752293577981</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="R4">
-        <v>1.109375</v>
+        <v>0.5352323838080959</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>0.06856266167681045</v>
+        <v>0.08135241227035207</v>
       </c>
       <c r="AB4">
-        <v>0.06856266167681045</v>
+        <v>0.08135241227035207</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -907,22 +901,22 @@
         <v>0</v>
       </c>
       <c r="AL4">
-        <v>35.7</v>
+        <v>32.5</v>
       </c>
       <c r="AM4">
-        <v>35.7</v>
+        <v>32.5</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>1.254901960784313</v>
+        <v>1.492307692307692</v>
       </c>
       <c r="AP4">
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1.254901960784313</v>
+        <v>1.492307692307692</v>
       </c>
     </row>
     <row r="5">
@@ -942,46 +936,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0445</v>
+        <v>0.0313</v>
       </c>
       <c r="E5">
-        <v>0.0555</v>
+        <v>0.0396</v>
       </c>
       <c r="G5">
-        <v>0.7835051546391752</v>
+        <v>0.71</v>
       </c>
       <c r="H5">
-        <v>0.7835051546391752</v>
+        <v>0.71</v>
       </c>
       <c r="I5">
-        <v>0.7113402061855671</v>
+        <v>0.74</v>
       </c>
       <c r="J5">
-        <v>0.5078638216255096</v>
+        <v>0.5012266666666667</v>
       </c>
       <c r="K5">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L5">
-        <v>0.1262886597938145</v>
+        <v>0.1275</v>
       </c>
       <c r="M5">
-        <v>0.624</v>
+        <v>1.33</v>
       </c>
       <c r="N5">
-        <v>0.0515702479338843</v>
+        <v>0.0880794701986755</v>
       </c>
       <c r="O5">
-        <v>0.2546938775510204</v>
+        <v>0.5215686274509804</v>
       </c>
       <c r="P5">
-        <v>0.624</v>
+        <v>1.33</v>
       </c>
       <c r="Q5">
-        <v>0.0515702479338843</v>
+        <v>0.0880794701986755</v>
       </c>
       <c r="R5">
-        <v>0.2546938775510204</v>
+        <v>0.5215686274509804</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -990,73 +984,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="V5">
-        <v>0.1619834710743802</v>
+        <v>0.08211920529801324</v>
       </c>
       <c r="W5">
-        <v>0.1195121951219512</v>
+        <v>0.125615763546798</v>
       </c>
       <c r="X5">
-        <v>0.3081643867956622</v>
+        <v>0.3644809460983172</v>
       </c>
       <c r="Y5">
-        <v>-0.188652191673711</v>
+        <v>-0.2388651825515191</v>
       </c>
       <c r="Z5">
-        <v>0.1254770066619235</v>
+        <v>0.1504438092372499</v>
       </c>
       <c r="AA5">
-        <v>0.06372523212945402</v>
+        <v>0.07540644902462264</v>
       </c>
       <c r="AB5">
-        <v>0.1451758106807816</v>
+        <v>0.1555554326315942</v>
       </c>
       <c r="AC5">
-        <v>-0.08145057855132762</v>
+        <v>-0.08014898360697158</v>
       </c>
       <c r="AD5">
-        <v>114.6</v>
+        <v>118.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>114.6</v>
+        <v>118.2</v>
       </c>
       <c r="AG5">
-        <v>112.64</v>
+        <v>116.96</v>
       </c>
       <c r="AH5">
-        <v>0.9044988161010261</v>
+        <v>0.886721680420105</v>
       </c>
       <c r="AI5">
-        <v>0.849518161601186</v>
+        <v>0.846704871060172</v>
       </c>
       <c r="AJ5">
-        <v>0.9029982363315697</v>
+        <v>0.8856580342268666</v>
       </c>
       <c r="AK5">
-        <v>0.8472995336241914</v>
+        <v>0.8453310205261636</v>
       </c>
       <c r="AL5">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="AM5">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="AN5">
-        <v>8.244604316546763</v>
+        <v>7.932885906040268</v>
       </c>
       <c r="AO5">
-        <v>1.326923076923077</v>
+        <v>1.345454545454545</v>
       </c>
       <c r="AP5">
-        <v>8.103597122302158</v>
+        <v>7.849664429530201</v>
       </c>
       <c r="AQ5">
-        <v>1.326923076923077</v>
+        <v>1.345454545454545</v>
       </c>
     </row>
     <row r="6">
@@ -1076,10 +1070,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.134</v>
+        <v>0.0924</v>
       </c>
       <c r="E6">
-        <v>0.134</v>
+        <v>0.11</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1094,28 +1088,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>3.86</v>
+        <v>3.51</v>
       </c>
       <c r="L6">
-        <v>0.4753694581280788</v>
+        <v>0.4588235294117646</v>
       </c>
       <c r="M6">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>0.04863636363636364</v>
+        <v>0.05794871794871794</v>
       </c>
       <c r="O6">
-        <v>0.2772020725388601</v>
+        <v>0.3219373219373219</v>
       </c>
       <c r="P6">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Q6">
-        <v>0.04863636363636364</v>
+        <v>0.05794871794871794</v>
       </c>
       <c r="R6">
-        <v>0.2772020725388601</v>
+        <v>0.3219373219373219</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,52 +1121,52 @@
         <v>17.3</v>
       </c>
       <c r="V6">
-        <v>0.7863636363636364</v>
+        <v>0.8871794871794872</v>
       </c>
       <c r="W6">
-        <v>0.116969696969697</v>
+        <v>0.1121405750798722</v>
       </c>
       <c r="X6">
-        <v>0.1781501348190846</v>
+        <v>0.264611467781335</v>
       </c>
       <c r="Y6">
-        <v>-0.06118043784938763</v>
+        <v>-0.1524708927014628</v>
       </c>
       <c r="Z6">
-        <v>0.07012089810017272</v>
+        <v>0.06999085086916744</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1294371176428483</v>
+        <v>0.1512410308043763</v>
       </c>
       <c r="AC6">
-        <v>-0.1294371176428483</v>
+        <v>-0.1512410308043763</v>
       </c>
       <c r="AD6">
-        <v>95.3</v>
+        <v>98.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>95.3</v>
+        <v>98.8</v>
       </c>
       <c r="AG6">
-        <v>78</v>
+        <v>81.5</v>
       </c>
       <c r="AH6">
-        <v>0.8124467178175618</v>
+        <v>0.8351648351648352</v>
       </c>
       <c r="AI6">
-        <v>0.7527646129541864</v>
+        <v>0.7462235649546827</v>
       </c>
       <c r="AJ6">
-        <v>0.78</v>
+        <v>0.806930693069307</v>
       </c>
       <c r="AK6">
-        <v>0.7136322049405307</v>
+        <v>0.7080799304952216</v>
       </c>
       <c r="AL6">
         <v>0</v>
